--- a/academias/Física - Estadisticos 20221.xlsx
+++ b/academias/Física - Estadisticos 20221.xlsx
@@ -796,25 +796,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>47.37</v>
+        <v>68.42</v>
       </c>
       <c r="H10" s="1">
-        <v>52.63</v>
+        <v>31.58</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -953,22 +953,25 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>70.97</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>29.03</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -985,22 +988,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>63.33</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>36.67</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1209,22 +1215,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1357,19 +1366,19 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>35.48</v>
+        <v>70.97</v>
       </c>
       <c r="H2" s="1">
-        <v>64.52</v>
+        <v>29.03</v>
       </c>
       <c r="I2" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -1392,19 +1401,19 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>53.33</v>
+        <v>63.33</v>
       </c>
       <c r="H3" s="1">
-        <v>46.67</v>
+        <v>36.67</v>
       </c>
       <c r="I3" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1637,25 +1646,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>47.37</v>
+        <v>78.95</v>
       </c>
       <c r="H10" s="1">
-        <v>52.63</v>
+        <v>21.05</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">

--- a/academias/Física - Estadisticos 20221.xlsx
+++ b/academias/Física - Estadisticos 20221.xlsx
@@ -1023,22 +1023,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1055,22 +1058,25 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>38.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.5</v>
       </c>
       <c r="J5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1087,22 +1093,25 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>78.38</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>21.62</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1119,22 +1128,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1151,22 +1163,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>11.54</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>88.45999999999999</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.6</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1183,22 +1198,25 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>76.92</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1250,22 +1268,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>27.78</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>72.22</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.5</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1282,22 +1303,25 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>44.44</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>55.56</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1436,19 +1460,19 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>88.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>11.43</v>
+        <v>14.29</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1471,19 +1495,19 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>80.95</v>
+        <v>61.9</v>
       </c>
       <c r="H5" s="1">
-        <v>19.05</v>
+        <v>38.1</v>
       </c>
       <c r="I5" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1518,7 +1542,7 @@
         <v>21.62</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1553,7 +1577,7 @@
         <v>15.63</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1576,19 +1600,19 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1">
-        <v>26.92</v>
+        <v>11.54</v>
       </c>
       <c r="H8" s="1">
-        <v>73.08</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="J8">
         <v>19</v>
@@ -1623,7 +1647,7 @@
         <v>76.92</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>20</v>
@@ -1681,19 +1705,19 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1">
-        <v>30.56</v>
+        <v>27.78</v>
       </c>
       <c r="H11" s="1">
-        <v>69.44</v>
+        <v>72.22</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>25</v>
@@ -1716,19 +1740,19 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="H12" s="1">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J12">
         <v>9</v>

--- a/academias/Física - Estadisticos 20221.xlsx
+++ b/academias/Física - Estadisticos 20221.xlsx
@@ -726,25 +726,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>26.92</v>
+        <v>46.15</v>
       </c>
       <c r="H8" s="1">
-        <v>73.08</v>
+        <v>53.85</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="J8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>73.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -761,25 +761,25 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>23.08</v>
+        <v>61.54</v>
       </c>
       <c r="H9" s="1">
-        <v>76.92</v>
+        <v>38.46</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>76.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -831,25 +831,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>30.56</v>
+        <v>80.56</v>
       </c>
       <c r="H11" s="1">
-        <v>69.44</v>
+        <v>19.44</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>69.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -866,25 +866,25 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="H12" s="1">
-        <v>50</v>
+        <v>22.22</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1163,25 +1163,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
-        <v>11.54</v>
+        <v>30.77</v>
       </c>
       <c r="H8" s="1">
-        <v>88.45999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="I8" s="2">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>73.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1198,25 +1198,25 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>23.08</v>
+        <v>61.54</v>
       </c>
       <c r="H9" s="1">
-        <v>76.92</v>
+        <v>38.46</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>76.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1268,25 +1268,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>27.78</v>
+        <v>77.78</v>
       </c>
       <c r="H11" s="1">
-        <v>72.22</v>
+        <v>22.22</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>69.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1303,25 +1303,25 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>44.44</v>
+        <v>72.22</v>
       </c>
       <c r="H12" s="1">
-        <v>55.56</v>
+        <v>27.78</v>
       </c>
       <c r="I12" s="2">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1600,25 +1600,25 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
-        <v>11.54</v>
+        <v>30.77</v>
       </c>
       <c r="H8" s="1">
-        <v>88.45999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="I8" s="2">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>73.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1635,25 +1635,25 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>23.08</v>
+        <v>61.54</v>
       </c>
       <c r="H9" s="1">
-        <v>76.92</v>
+        <v>38.46</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>76.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1705,25 +1705,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>27.78</v>
+        <v>77.78</v>
       </c>
       <c r="H11" s="1">
-        <v>72.22</v>
+        <v>22.22</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>69.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1740,25 +1740,25 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>44.44</v>
+        <v>72.22</v>
       </c>
       <c r="H12" s="1">
-        <v>55.56</v>
+        <v>27.78</v>
       </c>
       <c r="I12" s="2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20221.xlsx
+++ b/academias/Física - Estadisticos 20221.xlsx
@@ -66,6 +66,9 @@
     <t>5BEM</t>
   </si>
   <si>
+    <t>5APV</t>
+  </si>
+  <si>
     <t>5ALCM</t>
   </si>
   <si>
@@ -82,9 +85,6 @@
   </si>
   <si>
     <t>5ALCV</t>
-  </si>
-  <si>
-    <t>5APV</t>
   </si>
   <si>
     <t>5ARHV</t>
@@ -574,7 +574,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
@@ -583,22 +583,22 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>88.56999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="H4" s="1">
-        <v>11.43</v>
+        <v>31.58</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -618,22 +618,22 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>80.95</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>19.05</v>
+        <v>11.43</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -653,22 +653,22 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>78.38</v>
+        <v>80.95</v>
       </c>
       <c r="H6" s="1">
-        <v>21.62</v>
+        <v>19.05</v>
       </c>
       <c r="I6" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -688,22 +688,22 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>84.38</v>
+        <v>78.38</v>
       </c>
       <c r="H7" s="1">
-        <v>15.63</v>
+        <v>21.62</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -723,22 +723,22 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>46.15</v>
+        <v>84.38</v>
       </c>
       <c r="H8" s="1">
-        <v>53.85</v>
+        <v>15.63</v>
       </c>
       <c r="I8" s="2">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -761,19 +761,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1">
-        <v>61.54</v>
+        <v>46.15</v>
       </c>
       <c r="H9" s="1">
-        <v>38.46</v>
+        <v>53.85</v>
       </c>
       <c r="I9" s="2">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -793,22 +793,22 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>68.42</v>
+        <v>61.54</v>
       </c>
       <c r="H10" s="1">
-        <v>31.58</v>
+        <v>38.46</v>
       </c>
       <c r="I10" s="2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
@@ -1020,28 +1020,28 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>85.70999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H4" s="1">
-        <v>14.29</v>
+        <v>21.05</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1055,22 +1055,22 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>61.9</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>38.1</v>
+        <v>14.29</v>
       </c>
       <c r="I5" s="2">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1090,22 +1090,22 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>78.38</v>
+        <v>61.9</v>
       </c>
       <c r="H6" s="1">
-        <v>21.62</v>
+        <v>38.1</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1125,22 +1125,22 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>84.38</v>
+        <v>78.38</v>
       </c>
       <c r="H7" s="1">
-        <v>15.63</v>
+        <v>21.62</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1151,7 +1151,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -1160,22 +1160,22 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>30.77</v>
+        <v>84.38</v>
       </c>
       <c r="H8" s="1">
-        <v>69.23</v>
+        <v>15.63</v>
       </c>
       <c r="I8" s="2">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1198,19 +1198,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1">
-        <v>61.54</v>
+        <v>30.77</v>
       </c>
       <c r="H9" s="1">
-        <v>38.46</v>
+        <v>69.23</v>
       </c>
       <c r="I9" s="2">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1230,28 +1230,28 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>78.95</v>
+        <v>61.54</v>
       </c>
       <c r="H10" s="1">
-        <v>21.05</v>
+        <v>38.46</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1448,7 +1448,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
@@ -1457,22 +1457,22 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>85.70999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H4" s="1">
-        <v>14.29</v>
+        <v>21.05</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1492,22 +1492,22 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>61.9</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>38.1</v>
+        <v>14.29</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1527,22 +1527,22 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F6">
         <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>78.38</v>
+        <v>61.9</v>
       </c>
       <c r="H6" s="1">
-        <v>21.62</v>
+        <v>38.1</v>
       </c>
       <c r="I6" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1562,22 +1562,22 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>84.38</v>
+        <v>78.38</v>
       </c>
       <c r="H7" s="1">
-        <v>15.63</v>
+        <v>21.62</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -1597,22 +1597,22 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>30.77</v>
+        <v>84.38</v>
       </c>
       <c r="H8" s="1">
-        <v>69.23</v>
+        <v>15.63</v>
       </c>
       <c r="I8" s="2">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1635,19 +1635,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1">
-        <v>61.54</v>
+        <v>30.77</v>
       </c>
       <c r="H9" s="1">
-        <v>38.46</v>
+        <v>69.23</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1667,22 +1667,22 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>78.95</v>
+        <v>61.54</v>
       </c>
       <c r="H10" s="1">
-        <v>21.05</v>
+        <v>38.46</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
         <v>0</v>

--- a/academias/Física - Estadisticos 20221.xlsx
+++ b/academias/Física - Estadisticos 20221.xlsx
@@ -1635,19 +1635,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>30.77</v>
+        <v>34.62</v>
       </c>
       <c r="H9" s="1">
-        <v>69.23</v>
+        <v>65.38</v>
       </c>
       <c r="I9" s="2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1670,19 +1670,19 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1">
-        <v>61.54</v>
+        <v>53.85</v>
       </c>
       <c r="H10" s="1">
-        <v>38.46</v>
+        <v>46.15</v>
       </c>
       <c r="I10" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>22.22</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1740,19 +1740,19 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>72.22</v>
+        <v>55.56</v>
       </c>
       <c r="H12" s="1">
-        <v>27.78</v>
+        <v>44.44</v>
       </c>
       <c r="I12" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Física - Estadisticos 20221.xlsx
+++ b/academias/Física - Estadisticos 20221.xlsx
@@ -1390,19 +1390,19 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>70.97</v>
+        <v>58.06</v>
       </c>
       <c r="H2" s="1">
-        <v>29.03</v>
+        <v>41.94</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -1425,16 +1425,16 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>63.33</v>
+        <v>76.67</v>
       </c>
       <c r="H3" s="1">
-        <v>36.67</v>
+        <v>23.33</v>
       </c>
       <c r="I3" s="2">
         <v>6.4</v>
@@ -1472,7 +1472,7 @@
         <v>21.05</v>
       </c>
       <c r="I4" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>

--- a/academias/Física - Estadisticos 20221.xlsx
+++ b/academias/Física - Estadisticos 20221.xlsx
@@ -528,13 +528,13 @@
         <v>64.52</v>
       </c>
       <c r="I2" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -965,13 +965,13 @@
         <v>29.03</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1035,13 +1035,13 @@
         <v>21.05</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1402,13 +1402,13 @@
         <v>41.94</v>
       </c>
       <c r="I2" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1495,19 +1495,19 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>85.70999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>14.29</v>
+        <v>5.71</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1530,19 +1530,19 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>61.9</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>38.1</v>
+        <v>4.76</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1565,19 +1565,19 @@
         <v>37</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>78.38</v>
+        <v>97.3</v>
       </c>
       <c r="H7" s="1">
-        <v>21.62</v>
+        <v>2.7</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1600,19 +1600,19 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="H8" s="1">
-        <v>15.63</v>
+        <v>3.13</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
